--- a/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YJR007W</t>
+          <t>YKL081W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YPL237W</t>
+          <t>YER025W</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YKL081W</t>
+          <t>YDR140W</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YPL012W</t>
+          <t>YNR046W</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YDR140W</t>
+          <t>YPL012W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YER025W</t>
+          <t>YPL237W</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YNR046W</t>
+          <t>YJR007W</t>
         </is>
       </c>
     </row>

--- a/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YKL081W</t>
+          <t>YNR046W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YER025W</t>
+          <t>YJR007W</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YDR140W</t>
+          <t>YKL081W</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YNR046W</t>
+          <t>YER025W</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YGR285C</t>
+          <t>YLR249W</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YLR249W</t>
+          <t>YGR285C</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YPL012W</t>
+          <t>YDR077W</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YDR077W</t>
+          <t>YDR140W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YPL237W</t>
+          <t>YPL012W</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YJR007W</t>
+          <t>YPL237W</t>
         </is>
       </c>
     </row>

--- a/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YNR046W</t>
+          <t>YJR007W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YJR007W</t>
+          <t>YGR285C</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YKL081W</t>
+          <t>YDR077W</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YER025W</t>
+          <t>YLR249W</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YLR249W</t>
+          <t>YPL012W</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YGR285C</t>
+          <t>YPL237W</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YDR077W</t>
+          <t>YDR140W</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YDR140W</t>
+          <t>YNR046W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YPL012W</t>
+          <t>YKL081W</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YPL237W</t>
+          <t>YER025W</t>
         </is>
       </c>
     </row>

--- a/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YJR007W</t>
+          <t>YKL081W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YGR285C</t>
+          <t>YER025W</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YDR077W</t>
+          <t>YJR007W</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YLR249W</t>
+          <t>YPL237W</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YPL012W</t>
+          <t>YDR140W</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YPL237W</t>
+          <t>YLR249W</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YDR140W</t>
+          <t>YPL012W</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YNR046W</t>
+          <t>YDR077W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YKL081W</t>
+          <t>YGR285C</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YER025W</t>
+          <t>YNR046W</t>
         </is>
       </c>
     </row>

--- a/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YKL081W</t>
+          <t>YJR007W</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YJR007W</t>
+          <t>YDR077W</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YDR140W</t>
+          <t>YNR046W</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YLR249W</t>
+          <t>YDR140W</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YPL012W</t>
+          <t>YGR285C</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YDR077W</t>
+          <t>YKL081W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YGR285C</t>
+          <t>YPL012W</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YNR046W</t>
+          <t>YLR249W</t>
         </is>
       </c>
     </row>

--- a/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
+++ b/data/sce_compartment_curation/ribosome_annotations_v2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YJR007W</t>
+          <t>YDR077W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YER025W</t>
+          <t>YPL012W</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YDR077W</t>
+          <t>YNR046W</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YPL237W</t>
+          <t>YDR140W</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YNR046W</t>
+          <t>YLR249W</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YDR140W</t>
+          <t>YKL081W</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YGR285C</t>
+          <t>YER025W</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YKL081W</t>
+          <t>YPL237W</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YPL012W</t>
+          <t>YGR285C</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YLR249W</t>
+          <t>YJR007W</t>
         </is>
       </c>
     </row>
